--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/133.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/133.xlsx
@@ -426,13 +426,13 @@
         <v>-16.21359590358849</v>
       </c>
       <c r="E2">
-        <v>-10.01397514645933</v>
+        <v>-20.98027271460212</v>
       </c>
       <c r="F2">
-        <v>-1.935441650620621</v>
+        <v>-3.839698434747944</v>
       </c>
       <c r="G2">
-        <v>-5.192906070495956</v>
+        <v>-14.48823104853428</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.68206145752771</v>
       </c>
       <c r="E3">
-        <v>-10.78915932709234</v>
+        <v>-20.26372774389443</v>
       </c>
       <c r="F3">
-        <v>-2.510365904696604</v>
+        <v>-3.844335635468816</v>
       </c>
       <c r="G3">
-        <v>-5.603426262241203</v>
+        <v>-14.29937213862654</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.08426944544902</v>
       </c>
       <c r="E4">
-        <v>-11.71008338671421</v>
+        <v>-20.5877762869353</v>
       </c>
       <c r="F4">
-        <v>-2.184743790697549</v>
+        <v>-3.502109725248048</v>
       </c>
       <c r="G4">
-        <v>-5.468157903453094</v>
+        <v>-14.09350009493308</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.45990001164495</v>
       </c>
       <c r="E5">
-        <v>-11.68491865665359</v>
+        <v>-22.13919978264511</v>
       </c>
       <c r="F5">
-        <v>-2.114680475768767</v>
+        <v>-3.826450354874972</v>
       </c>
       <c r="G5">
-        <v>-5.326317257881418</v>
+        <v>-13.65903190763622</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.81173269438562</v>
       </c>
       <c r="E6">
-        <v>-13.01596396478012</v>
+        <v>-22.04768837989811</v>
       </c>
       <c r="F6">
-        <v>-2.006606694195126</v>
+        <v>-3.450497465849222</v>
       </c>
       <c r="G6">
-        <v>-4.616999187268457</v>
+        <v>-13.22795486282106</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.15606078133673</v>
       </c>
       <c r="E7">
-        <v>-13.01864482139266</v>
+        <v>-21.6351217554293</v>
       </c>
       <c r="F7">
-        <v>-1.298376587456231</v>
+        <v>-2.962478064368338</v>
       </c>
       <c r="G7">
-        <v>-4.428581601660463</v>
+        <v>-12.21715487410476</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.49163000310218</v>
       </c>
       <c r="E8">
-        <v>-13.50432365871531</v>
+        <v>-22.63373631512676</v>
       </c>
       <c r="F8">
-        <v>-1.110891364813215</v>
+        <v>-2.774089092888869</v>
       </c>
       <c r="G8">
-        <v>-3.340754936836197</v>
+        <v>-12.41197412297523</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.84132656215308</v>
       </c>
       <c r="E9">
-        <v>-13.10549189591176</v>
+        <v>-25.17646541348565</v>
       </c>
       <c r="F9">
-        <v>-0.9139934033721898</v>
+        <v>-2.784197660305231</v>
       </c>
       <c r="G9">
-        <v>-2.906672293072577</v>
+        <v>-11.47569067587391</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.20962003620392</v>
       </c>
       <c r="E10">
-        <v>-15.50178825875862</v>
+        <v>-24.62328061413066</v>
       </c>
       <c r="F10">
-        <v>-1.023765338121569</v>
+        <v>-2.991369034275776</v>
       </c>
       <c r="G10">
-        <v>-3.086302767344378</v>
+        <v>-11.27217618987092</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.59854642934928</v>
       </c>
       <c r="E11">
-        <v>-17.39646555577584</v>
+        <v>-25.43209324274464</v>
       </c>
       <c r="F11">
-        <v>-0.8232863443982412</v>
+        <v>-2.297299039920335</v>
       </c>
       <c r="G11">
-        <v>-2.05680637818236</v>
+        <v>-12.20884353989468</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.00606995375093</v>
       </c>
       <c r="E12">
-        <v>-17.135018637417</v>
+        <v>-27.62815859886835</v>
       </c>
       <c r="F12">
-        <v>-1.037160039024837</v>
+        <v>-2.342070641306842</v>
       </c>
       <c r="G12">
-        <v>-2.224483362313104</v>
+        <v>-10.26002761909368</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.422068279794264</v>
       </c>
       <c r="E13">
-        <v>-17.13174002223545</v>
+        <v>-26.42454002084365</v>
       </c>
       <c r="F13">
-        <v>-0.6679997627020431</v>
+        <v>-1.836426894963996</v>
       </c>
       <c r="G13">
-        <v>-0.3592893729545529</v>
+        <v>-9.217252126280592</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.857993362259712</v>
       </c>
       <c r="E14">
-        <v>-19.96784178070725</v>
+        <v>-27.10867470307844</v>
       </c>
       <c r="F14">
-        <v>-0.4749686202972855</v>
+        <v>-2.002711710667163</v>
       </c>
       <c r="G14">
-        <v>-0.5134674115897412</v>
+        <v>-9.613006821008337</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.316762851051486</v>
       </c>
       <c r="E15">
-        <v>-20.29954344482109</v>
+        <v>-27.62056887643149</v>
       </c>
       <c r="F15">
-        <v>-0.2138506475868253</v>
+        <v>-2.139023708634836</v>
       </c>
       <c r="G15">
-        <v>0.1776431605898615</v>
+        <v>-8.347721850584623</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.802360478669216</v>
       </c>
       <c r="E16">
-        <v>-21.2361360245095</v>
+        <v>-27.48291685202033</v>
       </c>
       <c r="F16">
-        <v>-0.04897654157062572</v>
+        <v>-1.777433882006227</v>
       </c>
       <c r="G16">
-        <v>1.051927926325466</v>
+        <v>-7.823336708283525</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.318587030950069</v>
       </c>
       <c r="E17">
-        <v>-21.54403602923902</v>
+        <v>-30.06664901828168</v>
       </c>
       <c r="F17">
-        <v>-0.05862205160882317</v>
+        <v>-1.732797304506375</v>
       </c>
       <c r="G17">
-        <v>0.6439638061750256</v>
+        <v>-7.789103723753838</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.861460117238565</v>
       </c>
       <c r="E18">
-        <v>-22.83911619679663</v>
+        <v>-30.32601510283399</v>
       </c>
       <c r="F18">
-        <v>0.2506514033285807</v>
+        <v>-1.758644852575928</v>
       </c>
       <c r="G18">
-        <v>1.410043728544821</v>
+        <v>-7.495732985345446</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.441304498587916</v>
       </c>
       <c r="E19">
-        <v>-23.75367322196372</v>
+        <v>-32.785569719094</v>
       </c>
       <c r="F19">
-        <v>0.2865105998283685</v>
+        <v>-0.9976684514637735</v>
       </c>
       <c r="G19">
-        <v>1.327570224648178</v>
+        <v>-8.348758716597407</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.059463364142294</v>
       </c>
       <c r="E20">
-        <v>-23.80633937467292</v>
+        <v>-31.32833848274373</v>
       </c>
       <c r="F20">
-        <v>0.03888756047691504</v>
+        <v>-1.561634233168122</v>
       </c>
       <c r="G20">
-        <v>1.890821436320899</v>
+        <v>-6.764079639577344</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.714643784049787</v>
       </c>
       <c r="E21">
-        <v>-24.48156202006062</v>
+        <v>-32.83283793078606</v>
       </c>
       <c r="F21">
-        <v>-0.03043519399376439</v>
+        <v>-1.380481050952106</v>
       </c>
       <c r="G21">
-        <v>2.857488995062669</v>
+        <v>-6.152181037064296</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.404586039362957</v>
       </c>
       <c r="E22">
-        <v>-26.19765894458536</v>
+        <v>-32.58027361419327</v>
       </c>
       <c r="F22">
-        <v>0.2582143977161401</v>
+        <v>-1.786943539790365</v>
       </c>
       <c r="G22">
-        <v>2.210822568905745</v>
+        <v>-6.934361913626288</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.121910273251367</v>
       </c>
       <c r="E23">
-        <v>-25.23028632706681</v>
+        <v>-33.58007010560673</v>
       </c>
       <c r="F23">
-        <v>0.6396320264981585</v>
+        <v>-2.027078966187914</v>
       </c>
       <c r="G23">
-        <v>2.654716065132104</v>
+        <v>-5.807508399573986</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.87107327086309</v>
       </c>
       <c r="E24">
-        <v>-25.4014898154008</v>
+        <v>-33.48160296678395</v>
       </c>
       <c r="F24">
-        <v>0.0709636030481175</v>
+        <v>-1.88731350451797</v>
       </c>
       <c r="G24">
-        <v>3.759834767574644</v>
+        <v>-5.06849199262649</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.652591474010043</v>
       </c>
       <c r="E25">
-        <v>-25.6039307174397</v>
+        <v>-32.9838217826758</v>
       </c>
       <c r="F25">
-        <v>0.7455147762913941</v>
+        <v>-1.64744398405672</v>
       </c>
       <c r="G25">
-        <v>3.422019883143573</v>
+        <v>-5.563004893850403</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.465983588601068</v>
       </c>
       <c r="E26">
-        <v>-26.92643532358776</v>
+        <v>-34.85545820394199</v>
       </c>
       <c r="F26">
-        <v>0.163208111921662</v>
+        <v>-1.728464114622331</v>
       </c>
       <c r="G26">
-        <v>3.762239902977717</v>
+        <v>-5.335534209241898</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.310421807700919</v>
       </c>
       <c r="E27">
-        <v>-25.52393069562019</v>
+        <v>-33.46068820957952</v>
       </c>
       <c r="F27">
-        <v>0.5754211272701548</v>
+        <v>-1.540351817855397</v>
       </c>
       <c r="G27">
-        <v>3.070811052306848</v>
+        <v>-5.487241488042825</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.181083958301224</v>
       </c>
       <c r="E28">
-        <v>-24.72866273276316</v>
+        <v>-35.11481523154629</v>
       </c>
       <c r="F28">
-        <v>0.2169161408495708</v>
+        <v>-1.455692669289287</v>
       </c>
       <c r="G28">
-        <v>3.627542476740952</v>
+        <v>-6.376226126364741</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.081528335651585</v>
       </c>
       <c r="E29">
-        <v>-26.25402486055883</v>
+        <v>-33.46545442847259</v>
       </c>
       <c r="F29">
-        <v>0.3876236101162845</v>
+        <v>-1.311430829356948</v>
       </c>
       <c r="G29">
-        <v>3.130650689886441</v>
+        <v>-6.361421254688526</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.012542598254419</v>
       </c>
       <c r="E30">
-        <v>-25.54692628663114</v>
+        <v>-33.52064067696707</v>
       </c>
       <c r="F30">
-        <v>0.03081594850403666</v>
+        <v>-1.504534039725749</v>
       </c>
       <c r="G30">
-        <v>2.894360081726149</v>
+        <v>-5.944673304423453</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.972416283953429</v>
       </c>
       <c r="E31">
-        <v>-25.43891312460019</v>
+        <v>-33.4437336028948</v>
       </c>
       <c r="F31">
-        <v>0.2186598542324638</v>
+        <v>-1.859732183474357</v>
       </c>
       <c r="G31">
-        <v>3.072802753793431</v>
+        <v>-5.306058995973406</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.958221722424732</v>
       </c>
       <c r="E32">
-        <v>-24.6509314764215</v>
+        <v>-30.88931424888511</v>
       </c>
       <c r="F32">
-        <v>0.08669181492507171</v>
+        <v>-1.419120248455689</v>
       </c>
       <c r="G32">
-        <v>2.51233401800312</v>
+        <v>-6.911153833536335</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.963140257778574</v>
       </c>
       <c r="E33">
-        <v>-24.32499908819343</v>
+        <v>-33.50821228005302</v>
       </c>
       <c r="F33">
-        <v>0.1431549938346916</v>
+        <v>-0.9274228957063755</v>
       </c>
       <c r="G33">
-        <v>2.355478502575424</v>
+        <v>-6.614459217688225</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.986834209188272</v>
       </c>
       <c r="E34">
-        <v>-24.831884769294</v>
+        <v>-31.33074536667881</v>
       </c>
       <c r="F34">
-        <v>0.09247630449882066</v>
+        <v>-1.897427870506152</v>
       </c>
       <c r="G34">
-        <v>2.588366483978572</v>
+        <v>-6.332201976701671</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.029473259889753</v>
       </c>
       <c r="E35">
-        <v>-23.67740466272653</v>
+        <v>-31.21672065540267</v>
       </c>
       <c r="F35">
-        <v>0.5516088779092803</v>
+        <v>-1.649157876213112</v>
       </c>
       <c r="G35">
-        <v>2.071301746976596</v>
+        <v>-6.566756818657018</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.090799340402439</v>
       </c>
       <c r="E36">
-        <v>-23.09772376195267</v>
+        <v>-30.19345534744446</v>
       </c>
       <c r="F36">
-        <v>-0.1757846803259796</v>
+        <v>-1.746275670517326</v>
       </c>
       <c r="G36">
-        <v>1.722852423471364</v>
+        <v>-7.941388497549227</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.17130433353919</v>
       </c>
       <c r="E37">
-        <v>-22.71591906141796</v>
+        <v>-29.53910217452111</v>
       </c>
       <c r="F37">
-        <v>0.3541948435763105</v>
+        <v>-1.360098242638822</v>
       </c>
       <c r="G37">
-        <v>1.636953324266661</v>
+        <v>-9.285307942645034</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.268944862437638</v>
       </c>
       <c r="E38">
-        <v>-21.02555745467882</v>
+        <v>-27.83491513663655</v>
       </c>
       <c r="F38">
-        <v>-0.06349036683507586</v>
+        <v>-1.342624660644169</v>
       </c>
       <c r="G38">
-        <v>1.233038231520576</v>
+        <v>-7.459150646179197</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.386785347950253</v>
       </c>
       <c r="E39">
-        <v>-19.67148938469729</v>
+        <v>-28.09254907988093</v>
       </c>
       <c r="F39">
-        <v>0.08391098555387377</v>
+        <v>-1.876731110947206</v>
       </c>
       <c r="G39">
-        <v>0.5051681342105141</v>
+        <v>-6.915980510450278</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.529242506894113</v>
       </c>
       <c r="E40">
-        <v>-19.93124718225127</v>
+        <v>-28.75140582020491</v>
       </c>
       <c r="F40">
-        <v>0.2764368238429237</v>
+        <v>-1.346070669039815</v>
       </c>
       <c r="G40">
-        <v>1.028050477037386</v>
+        <v>-7.973911965646443</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.698450658788558</v>
       </c>
       <c r="E41">
-        <v>-18.82643085012592</v>
+        <v>-26.03904461399269</v>
       </c>
       <c r="F41">
-        <v>0.3106202330868481</v>
+        <v>-1.328200299059221</v>
       </c>
       <c r="G41">
-        <v>0.05057785570036485</v>
+        <v>-6.84736688642073</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.895927385277036</v>
       </c>
       <c r="E42">
-        <v>-18.71337749652443</v>
+        <v>-26.68743605088494</v>
       </c>
       <c r="F42">
-        <v>0.5542198919629043</v>
+        <v>-0.9854069571675352</v>
       </c>
       <c r="G42">
-        <v>0.3465604464700754</v>
+        <v>-7.017317757092169</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.118684899462847</v>
       </c>
       <c r="E43">
-        <v>-17.73863705179541</v>
+        <v>-25.9271097934711</v>
       </c>
       <c r="F43">
-        <v>0.7230196311009708</v>
+        <v>-1.594779698056338</v>
       </c>
       <c r="G43">
-        <v>-0.2319943825558952</v>
+        <v>-7.924148959475905</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.366333037464502</v>
       </c>
       <c r="E44">
-        <v>-17.26386277988324</v>
+        <v>-26.51073046663164</v>
       </c>
       <c r="F44">
-        <v>0.9385873370662917</v>
+        <v>-1.469193401220114</v>
       </c>
       <c r="G44">
-        <v>-0.03183986742976753</v>
+        <v>-8.813845622876221</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.640414545681585</v>
       </c>
       <c r="E45">
-        <v>-15.89937921968407</v>
+        <v>-26.13367160685697</v>
       </c>
       <c r="F45">
-        <v>0.4315279108320611</v>
+        <v>-0.7911481742718288</v>
       </c>
       <c r="G45">
-        <v>0.7912250297629044</v>
+        <v>-8.685986262369338</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.93888579508356</v>
       </c>
       <c r="E46">
-        <v>-14.01280336266657</v>
+        <v>-25.03506381259615</v>
       </c>
       <c r="F46">
-        <v>0.7298520054392611</v>
+        <v>-1.052210646366301</v>
       </c>
       <c r="G46">
-        <v>-1.048952926426441</v>
+        <v>-8.741576718029451</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.258826669986046</v>
       </c>
       <c r="E47">
-        <v>-13.16090683234362</v>
+        <v>-23.99518126926679</v>
       </c>
       <c r="F47">
-        <v>0.6171037466116231</v>
+        <v>-0.7795990759419981</v>
       </c>
       <c r="G47">
-        <v>-1.044414997009729</v>
+        <v>-9.274945844960309</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.592616830161204</v>
       </c>
       <c r="E48">
-        <v>-12.84649035351706</v>
+        <v>-24.67869555056253</v>
       </c>
       <c r="F48">
-        <v>0.5689292119344151</v>
+        <v>-0.8986164192740227</v>
       </c>
       <c r="G48">
-        <v>-1.262612949491243</v>
+        <v>-8.50237566634593</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.934886915300543</v>
       </c>
       <c r="E49">
-        <v>-12.44371881832685</v>
+        <v>-23.48827747427019</v>
       </c>
       <c r="F49">
-        <v>1.105246574835524</v>
+        <v>-1.459009452370096</v>
       </c>
       <c r="G49">
-        <v>-1.652776442681695</v>
+        <v>-10.53832442565798</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.284046023209124</v>
       </c>
       <c r="E50">
-        <v>-11.1961468715837</v>
+        <v>-22.89703537935474</v>
       </c>
       <c r="F50">
-        <v>1.107347314569024</v>
+        <v>-0.5555306636891486</v>
       </c>
       <c r="G50">
-        <v>-0.8824046825121457</v>
+        <v>-9.211582175425871</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.634810435802628</v>
       </c>
       <c r="E51">
-        <v>-11.67288650121521</v>
+        <v>-19.79322382297148</v>
       </c>
       <c r="F51">
-        <v>0.8852835514309491</v>
+        <v>-1.107303705591691</v>
       </c>
       <c r="G51">
-        <v>-1.368028754531523</v>
+        <v>-9.569333762052128</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.981572251976687</v>
       </c>
       <c r="E52">
-        <v>-10.76384515738947</v>
+        <v>-20.93717975594512</v>
       </c>
       <c r="F52">
-        <v>1.030710075931625</v>
+        <v>-1.095828331960709</v>
       </c>
       <c r="G52">
-        <v>-2.008657733019069</v>
+        <v>-9.810277142383713</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.315028703395827</v>
       </c>
       <c r="E53">
-        <v>-9.272419413807279</v>
+        <v>-19.6768692118184</v>
       </c>
       <c r="F53">
-        <v>0.8711085284342439</v>
+        <v>-1.040733616000514</v>
       </c>
       <c r="G53">
-        <v>-2.184636207695208</v>
+        <v>-9.845793084543143</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.628453423898286</v>
       </c>
       <c r="E54">
-        <v>-9.108447898463544</v>
+        <v>-19.71830474898859</v>
       </c>
       <c r="F54">
-        <v>1.051740667553899</v>
+        <v>-0.6749605339877673</v>
       </c>
       <c r="G54">
-        <v>-1.793284912300237</v>
+        <v>-8.990516435301402</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.921442617578958</v>
       </c>
       <c r="E55">
-        <v>-8.520081384542966</v>
+        <v>-20.15671084614516</v>
       </c>
       <c r="F55">
-        <v>0.8226324680224169</v>
+        <v>-0.9638238444875942</v>
       </c>
       <c r="G55">
-        <v>-2.774612968969605</v>
+        <v>-10.46641317396119</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.190162982778732</v>
       </c>
       <c r="E56">
-        <v>-9.051280442590713</v>
+        <v>-19.41791748263779</v>
       </c>
       <c r="F56">
-        <v>0.8571621348407115</v>
+        <v>-1.236165367138585</v>
       </c>
       <c r="G56">
-        <v>-2.534732704423281</v>
+        <v>-10.15944505341046</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.430811867397612</v>
       </c>
       <c r="E57">
-        <v>-7.690261165007411</v>
+        <v>-19.19055638813468</v>
       </c>
       <c r="F57">
-        <v>1.164461590257244</v>
+        <v>-1.061525637810782</v>
       </c>
       <c r="G57">
-        <v>-3.489098963538692</v>
+        <v>-10.31793461717476</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.636087123381088</v>
       </c>
       <c r="E58">
-        <v>-7.587999164966199</v>
+        <v>-17.19119888595616</v>
       </c>
       <c r="F58">
-        <v>0.7301750687263528</v>
+        <v>-1.66631336512509</v>
       </c>
       <c r="G58">
-        <v>-2.417596375972664</v>
+        <v>-10.42570633929472</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.801172763852025</v>
       </c>
       <c r="E59">
-        <v>-5.898593066242672</v>
+        <v>-19.1405031649279</v>
       </c>
       <c r="F59">
-        <v>0.7007315777612473</v>
+        <v>-0.7470351249705467</v>
       </c>
       <c r="G59">
-        <v>-3.027736243729849</v>
+        <v>-11.76498941832704</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.928696242844566</v>
       </c>
       <c r="E60">
-        <v>-5.596471394346937</v>
+        <v>-16.91653335196893</v>
       </c>
       <c r="F60">
-        <v>0.5002086805655709</v>
+        <v>-0.8860691382238185</v>
       </c>
       <c r="G60">
-        <v>-4.191966152565786</v>
+        <v>-11.19655059536883</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.01774879179033</v>
       </c>
       <c r="E61">
-        <v>-5.017361081298036</v>
+        <v>-18.84807695588259</v>
       </c>
       <c r="F61">
-        <v>0.5085959005189159</v>
+        <v>-0.6291816378394555</v>
       </c>
       <c r="G61">
-        <v>-3.47433674774275</v>
+        <v>-12.12809923975987</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.06809970388904</v>
       </c>
       <c r="E62">
-        <v>-4.559464432012447</v>
+        <v>-17.96093531235794</v>
       </c>
       <c r="F62">
-        <v>0.6139750029312494</v>
+        <v>-1.115105269791257</v>
       </c>
       <c r="G62">
-        <v>-4.730933043477055</v>
+        <v>-11.49770439131623</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.07687125402546</v>
       </c>
       <c r="E63">
-        <v>-6.215962110122233</v>
+        <v>-18.93487421718761</v>
       </c>
       <c r="F63">
-        <v>0.6938710389312618</v>
+        <v>-2.042205783330435</v>
       </c>
       <c r="G63">
-        <v>-3.603406879005068</v>
+        <v>-10.91995346157232</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.04375253137828</v>
       </c>
       <c r="E64">
-        <v>-5.396593608596382</v>
+        <v>-16.16151446609207</v>
       </c>
       <c r="F64">
-        <v>0.3549378891366216</v>
+        <v>-2.368568457787593</v>
       </c>
       <c r="G64">
-        <v>-4.11464416651747</v>
+        <v>-12.53487555770579</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.97599027355233</v>
       </c>
       <c r="E65">
-        <v>-4.424715159440209</v>
+        <v>-16.62769369433769</v>
       </c>
       <c r="F65">
-        <v>0.3297008478429319</v>
+        <v>-2.261330498923377</v>
       </c>
       <c r="G65">
-        <v>-4.085145984698062</v>
+        <v>-11.70911349639125</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.87582140043461</v>
       </c>
       <c r="E66">
-        <v>-4.760573962693088</v>
+        <v>-16.78384453507018</v>
       </c>
       <c r="F66">
-        <v>0.1436420738675377</v>
+        <v>-1.767586250321746</v>
       </c>
       <c r="G66">
-        <v>-4.043389159132569</v>
+        <v>-10.64004885644389</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.745185133794951</v>
       </c>
       <c r="E67">
-        <v>-4.045632071784115</v>
+        <v>-16.52019677834361</v>
       </c>
       <c r="F67">
-        <v>0.05864660813589165</v>
+        <v>-1.671617401605215</v>
       </c>
       <c r="G67">
-        <v>-4.345176230840938</v>
+        <v>-11.90098620830134</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.582800498294125</v>
       </c>
       <c r="E68">
-        <v>-3.63352735166409</v>
+        <v>-14.25034446673892</v>
       </c>
       <c r="F68">
-        <v>-0.05992341679862119</v>
+        <v>-2.081969075399617</v>
       </c>
       <c r="G68">
-        <v>-4.275935893493535</v>
+        <v>-12.12608785094393</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.389124679708477</v>
       </c>
       <c r="E69">
-        <v>-3.196497910605847</v>
+        <v>-16.92977913844136</v>
       </c>
       <c r="F69">
-        <v>0.2527745089819558</v>
+        <v>-1.574092050538823</v>
       </c>
       <c r="G69">
-        <v>-3.648549925219908</v>
+        <v>-11.28689246856502</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.172049914120567</v>
       </c>
       <c r="E70">
-        <v>-2.615254686299333</v>
+        <v>-14.91264284730873</v>
       </c>
       <c r="F70">
-        <v>0.1300651321356538</v>
+        <v>-1.788710447460536</v>
       </c>
       <c r="G70">
-        <v>-3.514124840372577</v>
+        <v>-11.53930043702531</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.93415409733211</v>
       </c>
       <c r="E71">
-        <v>-4.561139967395285</v>
+        <v>-14.94541994217624</v>
       </c>
       <c r="F71">
-        <v>0.07689305691735636</v>
+        <v>-2.432015602270215</v>
       </c>
       <c r="G71">
-        <v>-3.539626494332581</v>
+        <v>-11.26725107631019</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.677867603046126</v>
       </c>
       <c r="E72">
-        <v>-5.119147591568442</v>
+        <v>-18.47443256550971</v>
       </c>
       <c r="F72">
-        <v>-0.3097002113973533</v>
+        <v>-2.044718221663126</v>
       </c>
       <c r="G72">
-        <v>-3.429288856953134</v>
+        <v>-11.77076436827166</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.403215064140605</v>
       </c>
       <c r="E73">
-        <v>-5.48605361261791</v>
+        <v>-15.74473183232212</v>
       </c>
       <c r="F73">
-        <v>0.007448532438465402</v>
+        <v>-2.354183029470577</v>
       </c>
       <c r="G73">
-        <v>-2.799599471144777</v>
+        <v>-10.6754204248547</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.111760820382694</v>
       </c>
       <c r="E74">
-        <v>-5.307532110287529</v>
+        <v>-17.25298538531681</v>
       </c>
       <c r="F74">
-        <v>-0.3356363947790059</v>
+        <v>-2.248488319077777</v>
       </c>
       <c r="G74">
-        <v>-3.464128867471318</v>
+        <v>-10.92284421776619</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.812805209398607</v>
       </c>
       <c r="E75">
-        <v>-4.821020033747472</v>
+        <v>-17.39284730504371</v>
       </c>
       <c r="F75">
-        <v>-0.3648272336862576</v>
+        <v>-2.412193598688626</v>
       </c>
       <c r="G75">
-        <v>-3.730393434577138</v>
+        <v>-9.650343841133258</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.509697398534814</v>
       </c>
       <c r="E76">
-        <v>-5.431204735437007</v>
+        <v>-17.61692525589126</v>
       </c>
       <c r="F76">
-        <v>-0.3151417568663433</v>
+        <v>-1.824073451886047</v>
       </c>
       <c r="G76">
-        <v>-3.078559084464088</v>
+        <v>-9.184439910686145</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.204797303485985</v>
       </c>
       <c r="E77">
-        <v>-6.221061171854871</v>
+        <v>-18.15049270584501</v>
       </c>
       <c r="F77">
-        <v>0.1044379297952455</v>
+        <v>-2.027544508668287</v>
       </c>
       <c r="G77">
-        <v>-1.422132816825207</v>
+        <v>-9.845248401764275</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.897728030503404</v>
       </c>
       <c r="E78">
-        <v>-6.11858180506129</v>
+        <v>-17.52819433618496</v>
       </c>
       <c r="F78">
-        <v>-0.446041202224124</v>
+        <v>-2.576474593644421</v>
       </c>
       <c r="G78">
-        <v>-1.622087177436208</v>
+        <v>-11.325584633194</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.587989526554024</v>
       </c>
       <c r="E79">
-        <v>-7.424702392249605</v>
+        <v>-18.21249657195804</v>
       </c>
       <c r="F79">
-        <v>-0.2157509224088474</v>
+        <v>-2.019518456902563</v>
       </c>
       <c r="G79">
-        <v>-1.389035134955088</v>
+        <v>-9.198490101403687</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.282409580068723</v>
       </c>
       <c r="E80">
-        <v>-7.722490314520001</v>
+        <v>-19.79109544018788</v>
       </c>
       <c r="F80">
-        <v>-0.2276868683157855</v>
+        <v>-1.803391602940352</v>
       </c>
       <c r="G80">
-        <v>-1.0939811298867</v>
+        <v>-10.39354052434749</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.982180648712196</v>
       </c>
       <c r="E81">
-        <v>-9.359633294721004</v>
+        <v>-19.37421317998976</v>
       </c>
       <c r="F81">
-        <v>-0.2724369321498203</v>
+        <v>-1.945890677039534</v>
       </c>
       <c r="G81">
-        <v>-0.6530571391716383</v>
+        <v>-8.412460351952467</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.688779870083095</v>
       </c>
       <c r="E82">
-        <v>-9.922739980626798</v>
+        <v>-19.10033107200586</v>
       </c>
       <c r="F82">
-        <v>-0.0597420043374081</v>
+        <v>-2.23613570436723</v>
       </c>
       <c r="G82">
-        <v>-0.07639885620702677</v>
+        <v>-8.974195639264725</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.402650617556502</v>
       </c>
       <c r="E83">
-        <v>-11.7058854913091</v>
+        <v>-22.31355961736244</v>
       </c>
       <c r="F83">
-        <v>0.001678953477966846</v>
+        <v>-2.956440922736735</v>
       </c>
       <c r="G83">
-        <v>-0.114487276069061</v>
+        <v>-9.18079775475516</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.124281732863301</v>
       </c>
       <c r="E84">
-        <v>-11.95046837246338</v>
+        <v>-21.43659798340704</v>
       </c>
       <c r="F84">
-        <v>-0.1640839907614366</v>
+        <v>-2.603738649972761</v>
       </c>
       <c r="G84">
-        <v>1.061522218165282</v>
+        <v>-7.787384363656689</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.861926341615466</v>
       </c>
       <c r="E85">
-        <v>-13.95898697755942</v>
+        <v>-25.14733826866832</v>
       </c>
       <c r="F85">
-        <v>-0.4591028994314665</v>
+        <v>-2.166638992741963</v>
       </c>
       <c r="G85">
-        <v>0.7917434627692966</v>
+        <v>-6.075528420214108</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.619065116778897</v>
       </c>
       <c r="E86">
-        <v>-14.37523977987047</v>
+        <v>-24.91920733358391</v>
       </c>
       <c r="F86">
-        <v>-0.2725694709342683</v>
+        <v>-1.883250362407238</v>
       </c>
       <c r="G86">
-        <v>0.8179997976879733</v>
+        <v>-5.803534840265498</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.399017407514898</v>
       </c>
       <c r="E87">
-        <v>-15.24673101722461</v>
+        <v>-25.65431451924903</v>
       </c>
       <c r="F87">
-        <v>-0.3230949123006213</v>
+        <v>-2.368632242077608</v>
       </c>
       <c r="G87">
-        <v>0.3915492752716219</v>
+        <v>-6.933935354823559</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.204047339946176</v>
       </c>
       <c r="E88">
-        <v>-18.26234601383447</v>
+        <v>-27.64835106446855</v>
       </c>
       <c r="F88">
-        <v>-0.1771829645019052</v>
+        <v>-2.452216169754884</v>
       </c>
       <c r="G88">
-        <v>1.850695377870449</v>
+        <v>-5.684790713250753</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.034352711086786</v>
       </c>
       <c r="E89">
-        <v>-19.12933594802499</v>
+        <v>-29.3072488338024</v>
       </c>
       <c r="F89">
-        <v>-0.265724671084936</v>
+        <v>-2.192078984049339</v>
       </c>
       <c r="G89">
-        <v>1.447603871735785</v>
+        <v>-6.902872030320296</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.897130860353684</v>
       </c>
       <c r="E90">
-        <v>-21.01423174118564</v>
+        <v>-28.55876453591861</v>
       </c>
       <c r="F90">
-        <v>-0.343733686141371</v>
+        <v>-2.316358117123946</v>
       </c>
       <c r="G90">
-        <v>2.030722879950943</v>
+        <v>-7.179830098488346</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.793949982329066</v>
       </c>
       <c r="E91">
-        <v>-23.1603842567968</v>
+        <v>-30.34725364592996</v>
       </c>
       <c r="F91">
-        <v>-0.2477507551789923</v>
+        <v>-2.095997477366027</v>
       </c>
       <c r="G91">
-        <v>1.817820819066373</v>
+        <v>-6.89948252844939</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.72528395659974</v>
       </c>
       <c r="E92">
-        <v>-24.79550300911638</v>
+        <v>-32.31303024910461</v>
       </c>
       <c r="F92">
-        <v>-0.2320051475865793</v>
+        <v>-2.81335536451637</v>
       </c>
       <c r="G92">
-        <v>1.992411337022866</v>
+        <v>-6.969211767809149</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.689999649511278</v>
       </c>
       <c r="E93">
-        <v>-26.88922485266674</v>
+        <v>-34.47375086559845</v>
       </c>
       <c r="F93">
-        <v>-0.1677172101901153</v>
+        <v>-2.545180529901462</v>
       </c>
       <c r="G93">
-        <v>1.743465057307796</v>
+        <v>-6.207623837754234</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.682991738163726</v>
       </c>
       <c r="E94">
-        <v>-27.88584688380082</v>
+        <v>-36.42440689406148</v>
       </c>
       <c r="F94">
-        <v>-0.832289869699269</v>
+        <v>-2.842487389338024</v>
       </c>
       <c r="G94">
-        <v>2.104415834954512</v>
+        <v>-5.976688183178955</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.705191788554316</v>
       </c>
       <c r="E95">
-        <v>-30.71773489720849</v>
+        <v>-37.87994448113288</v>
       </c>
       <c r="F95">
-        <v>-0.8024338517675692</v>
+        <v>-2.981867660165666</v>
       </c>
       <c r="G95">
-        <v>1.589710296253776</v>
+        <v>-5.348491753180145</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.753776310667639</v>
       </c>
       <c r="E96">
-        <v>-33.02745589397671</v>
+        <v>-37.8297101189658</v>
       </c>
       <c r="F96">
-        <v>-0.8367473146937332</v>
+        <v>-3.090522955656071</v>
       </c>
       <c r="G96">
-        <v>1.147667408986943</v>
+        <v>-6.379802657864536</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.821840633100608</v>
       </c>
       <c r="E97">
-        <v>-35.16339896493758</v>
+        <v>-41.84426346116467</v>
       </c>
       <c r="F97">
-        <v>-0.8222691092276034</v>
+        <v>-2.905005933962108</v>
       </c>
       <c r="G97">
-        <v>0.5776503184586479</v>
+        <v>-7.354371398121448</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.907770177685022</v>
       </c>
       <c r="E98">
-        <v>-36.16726881872094</v>
+        <v>-41.78852473884126</v>
       </c>
       <c r="F98">
-        <v>-1.001097892511363</v>
+        <v>-3.321039379772312</v>
       </c>
       <c r="G98">
-        <v>0.7579501619285756</v>
+        <v>-6.962367139636148</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.998283353580826</v>
       </c>
       <c r="E99">
-        <v>-39.39643985682153</v>
+        <v>-45.52101528476138</v>
       </c>
       <c r="F99">
-        <v>-1.498771087704473</v>
+        <v>-4.007566260557861</v>
       </c>
       <c r="G99">
-        <v>0.5587636071624841</v>
+        <v>-7.415175714839519</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.102349763611458</v>
       </c>
       <c r="E100">
-        <v>-40.88080570942576</v>
+        <v>-47.6791886346259</v>
       </c>
       <c r="F100">
-        <v>-1.457342777155664</v>
+        <v>-3.32222808699533</v>
       </c>
       <c r="G100">
-        <v>0.06942191111625584</v>
+        <v>-8.896758810461829</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.202684100918741</v>
       </c>
       <c r="E101">
-        <v>-43.7691751148941</v>
+        <v>-48.32219571592304</v>
       </c>
       <c r="F101">
-        <v>-1.444028427890468</v>
+        <v>-4.017876121253104</v>
       </c>
       <c r="G101">
-        <v>0.09144218900168934</v>
+        <v>-7.874737044012226</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.32193804866543</v>
       </c>
       <c r="E102">
-        <v>-46.01009953453779</v>
+        <v>-51.16096021711135</v>
       </c>
       <c r="F102">
-        <v>-1.65731812349809</v>
+        <v>-4.417876515982123</v>
       </c>
       <c r="G102">
-        <v>-0.3092376192867832</v>
+        <v>-9.129728822403964</v>
       </c>
     </row>
   </sheetData>
